--- a/output/laminas_comunales/comunal_s_fonasa_a_2024_los_lagos.xlsx
+++ b/output/laminas_comunales/comunal_s_fonasa_a_2024_los_lagos.xlsx
@@ -375,451 +375,451 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>10101</t>
+          <t>10306</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>San Juan de la Costa</t>
         </is>
       </c>
       <c r="C2">
-        <v>238941</v>
+        <v>95.30669144981412</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>10301</t>
+          <t>10102</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Osorno</t>
+          <t>Calbuco</t>
         </is>
       </c>
       <c r="C3">
-        <v>152662</v>
+        <v>95.18578685438746</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>10201</t>
+          <t>10104</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Castro</t>
+          <t>Fresia</t>
         </is>
       </c>
       <c r="C4">
-        <v>46312</v>
+        <v>93.21452048791177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>10202</t>
+          <t>10106</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Ancud</t>
+          <t>Los Muermos</t>
         </is>
       </c>
       <c r="C5">
-        <v>42799</v>
+        <v>93.02241316838345</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>10109</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Puerto Varas</t>
+          <t>Maullín</t>
         </is>
       </c>
       <c r="C6">
-        <v>42610</v>
+        <v>92.96254256526674</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>10102</t>
+          <t>10209</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Calbuco</t>
+          <t>Quemchi</t>
         </is>
       </c>
       <c r="C7">
-        <v>36914</v>
+        <v>92.52346531448916</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>10208</t>
+          <t>10207</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Quellón</t>
+          <t>Queilén</t>
         </is>
       </c>
       <c r="C8">
-        <v>29416</v>
+        <v>92.37426518615284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>10105</t>
+          <t>10303</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Frutillar</t>
+          <t>Purranque</t>
         </is>
       </c>
       <c r="C9">
-        <v>21313</v>
+        <v>92.07637455432538</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>10303</t>
+          <t>10205</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Purranque</t>
+          <t>Dalcahue</t>
         </is>
       </c>
       <c r="C10">
-        <v>19627</v>
+        <v>92.04716217778291</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>10107</t>
+          <t>10305</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Llanquihue</t>
+          <t>Río Negro</t>
         </is>
       </c>
       <c r="C11">
-        <v>18103</v>
+        <v>91.9800716932985</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>10106</t>
+          <t>10304</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Los Muermos</t>
+          <t>Puyehue</t>
         </is>
       </c>
       <c r="C12">
-        <v>17971</v>
+        <v>91.81614349775785</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>10205</t>
+          <t>10208</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Dalcahue</t>
+          <t>Quellón</t>
         </is>
       </c>
       <c r="C13">
-        <v>15926</v>
+        <v>91.18412895226287</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>10108</t>
+          <t>10403</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Maullín</t>
+          <t>Hualaihué</t>
         </is>
       </c>
       <c r="C14">
-        <v>15561</v>
+        <v>91.13630720847472</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>10203</t>
+          <t>10307</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Chonchi</t>
+          <t>San Pablo</t>
         </is>
       </c>
       <c r="C15">
-        <v>15412</v>
+        <v>90.82063659677176</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>10305</t>
+          <t>10302</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Río Negro</t>
+          <t>Puerto Octay</t>
         </is>
       </c>
       <c r="C16">
-        <v>15139</v>
+        <v>90.68962105471455</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>10304</t>
+          <t>10210</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Puyehue</t>
+          <t>Quinchao</t>
         </is>
       </c>
       <c r="C17">
-        <v>13923</v>
+        <v>90.44082979726544</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>10104</t>
+          <t>10404</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Fresia</t>
+          <t>Palena</t>
         </is>
       </c>
       <c r="C18">
-        <v>12762</v>
+        <v>89.98798558269924</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>10307</t>
+          <t>10401</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>San Pablo</t>
+          <t>Chaitén</t>
         </is>
       </c>
       <c r="C19">
-        <v>12041</v>
+        <v>89.78603148970529</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>10403</t>
+          <t>10402</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Hualaihué</t>
+          <t>Futaleufú</t>
         </is>
       </c>
       <c r="C20">
-        <v>11012</v>
+        <v>89.40435280641466</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>10302</t>
+          <t>10202</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Puerto Octay</t>
+          <t>Ancud</t>
         </is>
       </c>
       <c r="C21">
-        <v>9166</v>
+        <v>89.35073068893529</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>10209</t>
+          <t>10206</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Quemchi</t>
+          <t>Puqueldón</t>
         </is>
       </c>
       <c r="C22">
-        <v>8576</v>
+        <v>88.74013865646666</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>10306</t>
+          <t>10204</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>San Juan de la Costa</t>
+          <t>Curaco de Vélez</t>
         </is>
       </c>
       <c r="C23">
-        <v>8204</v>
+        <v>88.71660305343511</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>10210</t>
+          <t>10103</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Quinchao</t>
+          <t>Cochamó</t>
         </is>
       </c>
       <c r="C24">
-        <v>7673</v>
+        <v>88.59920459566946</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>10207</t>
+          <t>10203</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Queilén</t>
+          <t>Chonchi</t>
         </is>
       </c>
       <c r="C25">
-        <v>5657</v>
+        <v>88.51366873420629</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10107</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Chaitén</t>
+          <t>Llanquihue</t>
         </is>
       </c>
       <c r="C26">
-        <v>4448</v>
+        <v>87.78063327352956</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>10103</t>
+          <t>10105</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cochamó</t>
+          <t>Frutillar</t>
         </is>
       </c>
       <c r="C27">
-        <v>4010</v>
+        <v>86.17928915126764</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>10204</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Curaco de Vélez</t>
+          <t>Osorno</t>
         </is>
       </c>
       <c r="C28">
-        <v>3719</v>
+        <v>86.12320884576329</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>10206</t>
+          <t>10101</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Puqueldón</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="C29">
-        <v>3712</v>
+        <v>85.20977836421019</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>10402</t>
+          <t>10201</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Futaleufú</t>
+          <t>Castro</t>
         </is>
       </c>
       <c r="C30">
-        <v>3122</v>
+        <v>85.05261611357</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>10404</t>
+          <t>10109</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Palena</t>
+          <t>Puerto Varas</t>
         </is>
       </c>
       <c r="C31">
-        <v>2247</v>
+        <v>71.73521439754877</v>
       </c>
     </row>
   </sheetData>
@@ -875,7 +875,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Personas afiliadas a FONASA</t>
+          <t>Porcentaje de residentes afiliados a FONASA</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
